--- a/rules/CORE-000726/negative/02/data/unit-test-coreid-FB5701-negative_02.xlsx
+++ b/rules/CORE-000726/negative/02/data/unit-test-coreid-FB5701-negative_02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\verisian\core-contributor\rules\CORE-000726\negative\02\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEBFEAA3-58C4-4EEB-87B4-41F481E3EE7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18F26690-26AA-4011-8D5F-627EA4EF3B9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="99">
   <si>
     <t>Product</t>
   </si>
@@ -323,9 +323,6 @@
   </si>
   <si>
     <t>S005</t>
-  </si>
-  <si>
-    <t>[ABSENT]</t>
   </si>
 </sst>
 </file>
@@ -425,7 +422,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -462,6 +459,9 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -827,7 +827,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="21.85546875" customWidth="1"/>
@@ -922,13 +922,13 @@
         <v>95</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" t="s">
         <v>29</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -942,7 +942,7 @@
         <v>95</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" t="s">
         <v>91</v>
@@ -954,19 +954,19 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
         <v>95</v>
       </c>
       <c r="D7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E7" t="s">
         <v>80</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -980,14 +980,12 @@
         <v>95</v>
       </c>
       <c r="D8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="10" t="s">
-        <v>94</v>
-      </c>
+      <c r="F8" s="10"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
@@ -1000,7 +998,7 @@
         <v>95</v>
       </c>
       <c r="D9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" t="s">
         <v>91</v>
@@ -1018,68 +1016,12 @@
         <v>95</v>
       </c>
       <c r="D10">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E10" t="s">
         <v>80</v>
       </c>
-      <c r="F10" s="10" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>4</v>
-      </c>
-      <c r="B11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" t="s">
-        <v>95</v>
-      </c>
-      <c r="D11">
-        <v>9</v>
-      </c>
-      <c r="E11" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" s="10"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>4</v>
-      </c>
-      <c r="B12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" t="s">
-        <v>95</v>
-      </c>
-      <c r="D12">
-        <v>9</v>
-      </c>
-      <c r="E12" t="s">
-        <v>91</v>
-      </c>
-      <c r="F12" s="10"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>4</v>
-      </c>
-      <c r="B13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" t="s">
-        <v>95</v>
-      </c>
-      <c r="D13">
-        <v>9</v>
-      </c>
-      <c r="E13" t="s">
-        <v>80</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="F10" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1393,7 +1335,7 @@
       <c r="M7" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="N7" s="14" t="s">
+      <c r="N7" s="16" t="s">
         <v>97</v>
       </c>
     </row>
